--- a/progLinear/exercicios/Modelagem_solucao_grafica_e_Simplex_Form2.xlsx
+++ b/progLinear/exercicios/Modelagem_solucao_grafica_e_Simplex_Form2.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/29ef9a7b83f2ddc4/Arquivo_pessoal/CLIENTES/IBMEC/ENSINO/Disciplina Programação Linear/"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1436" documentId="8_{DE438C06-8D59-460A-A782-4FCA6206D474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE0F6D3F-E32F-4CED-BBDF-054A3C3622D1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{BC4CC188-7A29-4ECC-830A-209069F6CA88}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="4" xr2:uid="{BC4CC188-7A29-4ECC-830A-209069F6CA88}"/>
   </bookViews>
   <sheets>
     <sheet name="Questão1" sheetId="1" r:id="rId1"/>
@@ -199,7 +199,7 @@
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -226,12 +226,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="29">
   <si>
     <t>x2</t>
-  </si>
-  <si>
-    <t>x1</t>
-  </si>
-  <si>
-    <t>x3</t>
   </si>
   <si>
     <t>x1A</t>
@@ -270,6 +264,12 @@
     <t>x4P</t>
   </si>
   <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
     <t>Máx</t>
   </si>
   <si>
@@ -291,19 +291,19 @@
     <t>bi</t>
   </si>
   <si>
+    <t>PIVÔ</t>
+  </si>
+  <si>
+    <t>QUADRO 0</t>
+  </si>
+  <si>
     <t>Zi</t>
   </si>
   <si>
     <t>Ci-Zi</t>
   </si>
   <si>
-    <t>QUADRO 0</t>
-  </si>
-  <si>
     <t>QUADRO 1</t>
-  </si>
-  <si>
-    <t>PIVÔ</t>
   </si>
   <si>
     <t>QUADRO 2</t>
@@ -319,7 +319,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4322,8 +4322,8 @@
       <xdr:rowOff>163830</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="800100" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="CaixaDeTexto 1">
@@ -4365,9 +4365,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
                       <a:rPr lang="pt-BR" sz="1400" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -4413,7 +4417,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4426,7 +4430,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4456,7 +4460,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="CaixaDeTexto 1">
@@ -4544,8 +4548,8 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1402080" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="CaixaDeTexto 2">
@@ -4587,9 +4591,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
                       <a:rPr lang="pt-BR" sz="1400" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -4635,7 +4643,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4648,7 +4656,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4690,7 +4698,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="CaixaDeTexto 2">
@@ -4790,8 +4798,8 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1402080" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="CaixaDeTexto 3">
@@ -4833,9 +4841,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
                       <a:rPr lang="pt-BR" sz="1400" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -4881,7 +4893,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4894,7 +4906,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -4936,7 +4948,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="CaixaDeTexto 3">
@@ -5036,8 +5048,8 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1691640" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="CaixaDeTexto 4">
@@ -5079,9 +5091,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
                       <a:rPr lang="pt-BR" sz="1400" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -5127,7 +5143,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5140,7 +5156,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5209,7 +5225,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5249,7 +5265,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="5" name="CaixaDeTexto 4">
@@ -5385,8 +5401,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1668780" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CaixaDeTexto 5">
@@ -5428,9 +5444,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
                       <a:rPr lang="pt-BR" sz="1400" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -5476,7 +5496,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5489,7 +5509,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5586,7 +5606,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CaixaDeTexto 5">
@@ -5691,8 +5711,8 @@
       <xdr:rowOff>163830</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="2141220" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="CaixaDeTexto 1">
@@ -5734,9 +5754,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
                       <a:rPr lang="pt-BR" sz="1400" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -5782,7 +5806,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5795,7 +5819,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -5880,7 +5904,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="CaixaDeTexto 1">
@@ -5968,8 +5992,8 @@
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1874520" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="CaixaDeTexto 2">
@@ -6011,9 +6035,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:r>
                       <a:rPr lang="pt-BR" sz="1400" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -6059,7 +6087,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6072,7 +6100,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6169,7 +6197,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="3" name="CaixaDeTexto 2">
@@ -6269,8 +6297,8 @@
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1874520" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="CaixaDeTexto 3">
@@ -6312,9 +6340,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -6354,7 +6386,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6367,7 +6399,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6464,7 +6496,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="4" name="CaixaDeTexto 3">
@@ -6564,8 +6596,8 @@
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1874520" cy="221214"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CaixaDeTexto 6">
@@ -6607,9 +6639,13 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMath>
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                     <m:sSub>
                       <m:sSubPr>
                         <m:ctrlPr>
@@ -6649,7 +6685,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6662,7 +6698,7 @@
                               <a:schemeClr val="tx1"/>
                             </a:solidFill>
                             <a:effectLst/>
-                            <a:latin typeface="+mn-lt"/>
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                             <a:ea typeface="+mn-ea"/>
                             <a:cs typeface="+mn-cs"/>
                           </a:rPr>
@@ -6771,7 +6807,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="CaixaDeTexto 6">
@@ -7184,9 +7220,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9AFB7B-C032-4B91-9D84-5D9EE7F5A916}">
   <dimension ref="B3:F63"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -7200,7 +7236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6">
       <c r="B4">
         <v>0</v>
       </c>
@@ -7220,7 +7256,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6">
       <c r="B5">
         <f>B4+0.5</f>
         <v>0.5</v>
@@ -7241,7 +7277,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6">
       <c r="B6">
         <f t="shared" ref="B6:B63" si="3">B5+0.5</f>
         <v>1</v>
@@ -7262,7 +7298,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6">
       <c r="B7">
         <f t="shared" si="3"/>
         <v>1.5</v>
@@ -7283,7 +7319,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6">
       <c r="B8">
         <f t="shared" si="3"/>
         <v>2</v>
@@ -7304,7 +7340,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6">
       <c r="B9">
         <f t="shared" si="3"/>
         <v>2.5</v>
@@ -7325,7 +7361,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6">
       <c r="B10">
         <f t="shared" si="3"/>
         <v>3</v>
@@ -7346,7 +7382,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6">
       <c r="B11">
         <f t="shared" si="3"/>
         <v>3.5</v>
@@ -7367,7 +7403,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6">
       <c r="B12">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -7388,7 +7424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6">
       <c r="B13">
         <f t="shared" si="3"/>
         <v>4.5</v>
@@ -7409,7 +7445,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6">
       <c r="B14">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -7430,7 +7466,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6">
       <c r="B15">
         <f t="shared" si="3"/>
         <v>5.5</v>
@@ -7451,7 +7487,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6">
       <c r="B16">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -7472,7 +7508,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6">
       <c r="B17">
         <f t="shared" si="3"/>
         <v>6.5</v>
@@ -7493,7 +7529,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6">
       <c r="B18">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -7514,7 +7550,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6">
       <c r="B19">
         <f t="shared" si="3"/>
         <v>7.5</v>
@@ -7535,7 +7571,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6">
       <c r="B20">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -7556,7 +7592,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6">
       <c r="B21">
         <f t="shared" si="3"/>
         <v>8.5</v>
@@ -7577,7 +7613,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6">
       <c r="B22">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -7598,7 +7634,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6">
       <c r="B23">
         <f t="shared" si="3"/>
         <v>9.5</v>
@@ -7619,7 +7655,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6">
       <c r="B24">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -7640,7 +7676,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6">
       <c r="B25">
         <f t="shared" si="3"/>
         <v>10.5</v>
@@ -7661,7 +7697,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6">
       <c r="B26">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -7682,7 +7718,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6">
       <c r="B27">
         <f t="shared" si="3"/>
         <v>11.5</v>
@@ -7703,7 +7739,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6">
       <c r="B28">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -7724,7 +7760,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6">
       <c r="B29">
         <f t="shared" si="3"/>
         <v>12.5</v>
@@ -7745,7 +7781,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6">
       <c r="B30">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -7766,7 +7802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6">
       <c r="B31">
         <f t="shared" si="3"/>
         <v>13.5</v>
@@ -7787,7 +7823,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6">
       <c r="B32">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -7808,7 +7844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:6">
       <c r="B33">
         <f t="shared" si="3"/>
         <v>14.5</v>
@@ -7829,7 +7865,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:6">
       <c r="B34">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -7850,7 +7886,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:6">
       <c r="B35">
         <f t="shared" si="3"/>
         <v>15.5</v>
@@ -7871,7 +7907,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6">
       <c r="B36">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -7892,7 +7928,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:6">
       <c r="B37">
         <f t="shared" si="3"/>
         <v>16.5</v>
@@ -7913,7 +7949,7 @@
         <v>-5.5</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:6">
       <c r="B38">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -7934,7 +7970,7 @@
         <v>-7</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:6">
       <c r="B39">
         <f t="shared" si="3"/>
         <v>17.5</v>
@@ -7955,7 +7991,7 @@
         <v>-8.5</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:6">
       <c r="B40">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -7976,7 +8012,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:6">
       <c r="B41">
         <f t="shared" si="3"/>
         <v>18.5</v>
@@ -7997,7 +8033,7 @@
         <v>-11.5</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:6">
       <c r="B42">
         <f t="shared" si="3"/>
         <v>19</v>
@@ -8018,7 +8054,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:6">
       <c r="B43">
         <f t="shared" si="3"/>
         <v>19.5</v>
@@ -8039,7 +8075,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:6">
       <c r="B44">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -8060,7 +8096,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:6">
       <c r="B45">
         <f t="shared" si="3"/>
         <v>20.5</v>
@@ -8081,7 +8117,7 @@
         <v>-17.5</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:6">
       <c r="B46">
         <f t="shared" si="3"/>
         <v>21</v>
@@ -8102,7 +8138,7 @@
         <v>-19</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:6">
       <c r="B47">
         <f t="shared" si="3"/>
         <v>21.5</v>
@@ -8123,7 +8159,7 @@
         <v>-20.5</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:6">
       <c r="B48">
         <f t="shared" si="3"/>
         <v>22</v>
@@ -8144,7 +8180,7 @@
         <v>-22</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:6">
       <c r="B49">
         <f t="shared" si="3"/>
         <v>22.5</v>
@@ -8165,7 +8201,7 @@
         <v>-23.5</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:6">
       <c r="B50">
         <f t="shared" si="3"/>
         <v>23</v>
@@ -8186,7 +8222,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:6">
       <c r="B51">
         <f t="shared" si="3"/>
         <v>23.5</v>
@@ -8207,7 +8243,7 @@
         <v>-26.5</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:6">
       <c r="B52">
         <f t="shared" si="3"/>
         <v>24</v>
@@ -8228,7 +8264,7 @@
         <v>-28</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:6">
       <c r="B53">
         <f t="shared" si="3"/>
         <v>24.5</v>
@@ -8249,7 +8285,7 @@
         <v>-29.5</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:6">
       <c r="B54">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -8270,7 +8306,7 @@
         <v>-31</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:6">
       <c r="B55">
         <f t="shared" si="3"/>
         <v>25.5</v>
@@ -8291,7 +8327,7 @@
         <v>-32.5</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:6">
       <c r="B56">
         <f t="shared" si="3"/>
         <v>26</v>
@@ -8312,7 +8348,7 @@
         <v>-34</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:6">
       <c r="B57">
         <f t="shared" si="3"/>
         <v>26.5</v>
@@ -8333,7 +8369,7 @@
         <v>-35.5</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:6">
       <c r="B58">
         <f t="shared" si="3"/>
         <v>27</v>
@@ -8354,7 +8390,7 @@
         <v>-37</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:6">
       <c r="B59">
         <f t="shared" si="3"/>
         <v>27.5</v>
@@ -8375,7 +8411,7 @@
         <v>-38.5</v>
       </c>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:6">
       <c r="B60">
         <f t="shared" si="3"/>
         <v>28</v>
@@ -8396,7 +8432,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:6">
       <c r="B61">
         <f t="shared" si="3"/>
         <v>28.5</v>
@@ -8417,7 +8453,7 @@
         <v>-41.5</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:6">
       <c r="B62">
         <f t="shared" si="3"/>
         <v>29</v>
@@ -8438,7 +8474,7 @@
         <v>-43</v>
       </c>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:6">
       <c r="B63">
         <f t="shared" si="3"/>
         <v>29.5</v>
@@ -8468,55 +8504,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E14A471-6EBF-4A59-A9C2-2AA5FE75C511}">
   <dimension ref="F9:W21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19" customWidth="1"/>
-    <col min="23" max="23" width="15.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="6:23" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="6:23" ht="18">
       <c r="F9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F10" s="2">
         <v>1</v>
       </c>
@@ -8561,7 +8597,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F11" s="2">
         <v>0</v>
       </c>
@@ -8606,7 +8642,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F12" s="2">
         <v>0</v>
       </c>
@@ -8651,7 +8687,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F13" s="2">
         <v>500</v>
       </c>
@@ -8696,7 +8732,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="14" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F14" s="2">
         <v>0</v>
       </c>
@@ -8741,7 +8777,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="15" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="15" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F15" s="2">
         <v>0</v>
       </c>
@@ -8786,7 +8822,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="16" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="16" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F16" s="2">
         <v>1</v>
       </c>
@@ -8831,7 +8867,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="17" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F17" s="2">
         <v>0</v>
       </c>
@@ -8876,7 +8912,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="18" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F18" s="2">
         <v>0</v>
       </c>
@@ -8921,7 +8957,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="6:23" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="19" spans="6:23" s="3" customFormat="1" ht="18">
       <c r="F19" s="2">
         <v>0</v>
       </c>
@@ -8966,7 +9002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="6:23" ht="18" x14ac:dyDescent="0.35">
+    <row r="21" spans="6:23" ht="18">
       <c r="F21" s="2">
         <v>7.0000000000000009</v>
       </c>
@@ -9017,27 +9053,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC17734C-FF9D-4DC7-86DB-F523C72778AF}">
   <dimension ref="F9:N14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="6:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="6:14" ht="18">
       <c r="F9" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="6:14" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="6:14" s="3" customFormat="1" ht="18">
       <c r="F10" s="2">
         <v>6</v>
       </c>
@@ -9055,7 +9091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="6:14" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="6:14" s="3" customFormat="1" ht="18">
       <c r="F11" s="2">
         <v>2</v>
       </c>
@@ -9073,7 +9109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="6:14" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="6:14" s="3" customFormat="1" ht="18">
       <c r="F12" s="2">
         <v>4</v>
       </c>
@@ -9091,7 +9127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="6:14" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="6:14" ht="18">
       <c r="F14" s="2">
         <v>0</v>
       </c>
@@ -9115,23 +9151,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0202BAED-84CB-4A17-BA37-0F264C119E58}">
   <dimension ref="F9:M13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="13" max="13" width="15.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="6:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="6:13" ht="18">
       <c r="F9" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="6:13" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="6:13" s="3" customFormat="1" ht="18">
       <c r="F10" s="2">
         <f>5000/400</f>
         <v>12.5</v>
@@ -9148,7 +9184,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="11" spans="6:13" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="6:13" s="3" customFormat="1" ht="18">
       <c r="F11" s="2">
         <v>1</v>
       </c>
@@ -9163,7 +9199,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="13" spans="6:13" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="6:13" ht="18">
       <c r="F13" s="2">
         <v>266.66666666666669</v>
       </c>
@@ -9184,35 +9220,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F3F28A5-59B9-4F79-8016-14899E402055}">
   <dimension ref="B3:N27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14">
       <c r="C3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14">
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" ht="15.6">
       <c r="D11" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" ht="15" thickBot="1"/>
+    <row r="13" spans="2:14">
       <c r="D13" s="23"/>
       <c r="E13" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>0</v>
@@ -9227,7 +9263,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14">
       <c r="D14" s="24" t="s">
         <v>19</v>
       </c>
@@ -9254,12 +9290,12 @@
         <v>10</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>20</v>
@@ -9287,10 +9323,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:14">
       <c r="D16" s="24"/>
       <c r="E16" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F16" s="11">
         <v>0</v>
@@ -9308,10 +9344,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" ht="15" thickBot="1">
       <c r="D17" s="25"/>
       <c r="E17" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F17" s="15">
         <v>8</v>
@@ -9327,13 +9363,13 @@
       </c>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:14">
       <c r="D18" s="23"/>
       <c r="E18" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>0</v>
@@ -9348,9 +9384,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:14">
       <c r="D19" s="24" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E19" s="26">
         <v>8</v>
@@ -9381,9 +9417,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:14">
       <c r="B20" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D20" s="24" t="s">
         <v>20</v>
@@ -9420,13 +9456,13 @@
         <v>6</v>
       </c>
       <c r="N20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
       <c r="D21" s="24"/>
       <c r="E21" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F21" s="11">
         <f>E19*F19+E20*F20</f>
@@ -9449,10 +9485,10 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" ht="15" thickBot="1">
       <c r="D22" s="25"/>
       <c r="E22" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F22" s="18">
         <f>F17-F21</f>
@@ -9472,13 +9508,13 @@
       </c>
       <c r="J22" s="28"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:14">
       <c r="D23" s="23"/>
       <c r="E23" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G23" s="21" t="s">
         <v>0</v>
@@ -9493,9 +9529,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14">
       <c r="D24" s="24" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E24" s="26">
         <v>8</v>
@@ -9525,7 +9561,7 @@
         <v>-0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:14">
       <c r="B25" s="12" t="s">
         <v>27</v>
       </c>
@@ -9557,10 +9593,10 @@
       <c r="K25" s="20"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:14">
       <c r="D26" s="24"/>
       <c r="E26" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F26" s="11">
         <f>E24*F24+E25*F25</f>
@@ -9583,10 +9619,10 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" ht="15" thickBot="1">
       <c r="D27" s="25"/>
       <c r="E27" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F27" s="18">
         <f>F17-F26</f>
@@ -9618,43 +9654,43 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2876673-DEF0-48A7-B604-36339FA1B3A4}">
   <dimension ref="B3:O25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="10.5546875" customWidth="1"/>
-    <col min="7" max="7" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
     <col min="8" max="8" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:15">
       <c r="C3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:15">
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:15" ht="28.2" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="2:15" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" ht="28.15" customHeight="1"/>
+    <row r="11" spans="2:15" ht="15.6">
       <c r="D11" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" ht="15" thickBot="1"/>
+    <row r="13" spans="2:15">
       <c r="D13" s="23"/>
       <c r="E13" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>0</v>
       </c>
       <c r="H13" s="21" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I13" s="21" t="s">
         <v>19</v>
@@ -9669,7 +9705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15">
       <c r="D14" s="24" t="s">
         <v>19</v>
       </c>
@@ -9702,9 +9738,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15">
       <c r="B15" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>20</v>
@@ -9738,10 +9774,10 @@
         <v>10</v>
       </c>
       <c r="O15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15">
       <c r="B16" s="12"/>
       <c r="D16" s="24" t="s">
         <v>28</v>
@@ -9775,10 +9811,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="4:13">
       <c r="D17" s="24"/>
       <c r="E17" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F17" s="11">
         <v>0</v>
@@ -9802,10 +9838,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="4:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="4:13" ht="15" thickBot="1">
       <c r="D18" s="25"/>
       <c r="E18" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F18" s="18">
         <v>40</v>
@@ -9827,7 +9863,7 @@
       </c>
       <c r="L18" s="28"/>
     </row>
-    <row r="19" spans="4:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="4:13" ht="15" thickBot="1">
       <c r="F19" s="30"/>
       <c r="G19" s="30"/>
       <c r="H19" s="30"/>
@@ -9836,19 +9872,19 @@
       <c r="K19" s="30"/>
       <c r="L19" s="30"/>
     </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="4:13">
       <c r="D20" s="23"/>
       <c r="E20" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>0</v>
       </c>
       <c r="H20" s="21" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I20" s="21" t="s">
         <v>19</v>
@@ -9863,7 +9899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="4:13">
       <c r="D21" s="24" t="s">
         <v>19</v>
       </c>
@@ -9903,7 +9939,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="4:13">
       <c r="D22" s="24" t="s">
         <v>0</v>
       </c>
@@ -9938,7 +9974,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:13">
       <c r="D23" s="24" t="s">
         <v>28</v>
       </c>
@@ -9978,10 +10014,10 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="4:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:13">
       <c r="D24" s="24"/>
       <c r="E24" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F24" s="11">
         <f>E21*F21+E22*F22+E23*F23</f>
@@ -9994,10 +10030,10 @@
       <c r="K24" s="32"/>
       <c r="L24" s="17"/>
     </row>
-    <row r="25" spans="4:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="4:13" ht="15" thickBot="1">
       <c r="D25" s="25"/>
       <c r="E25" s="27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
